--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -663,7 +663,7 @@
   &lt;coding&gt;
     &lt;system value="https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis"/&gt;
     &lt;code value="GEN-295"/&gt;
-    &lt;display value="En rapport avec la prévention"/&gt;
+    &lt;display value="En rapport avec la prevention"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-prevention-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
